--- a/gex_pivot_levels_2026-07-08.xlsx
+++ b/gex_pivot_levels_2026-07-08.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,6 +91,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -98,15 +107,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7447.4</v>
+        <v>7437.4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7400</v>
+        <v>7390</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -544,31 +544,27 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$6.89M</t>
+          <t>-$7.78M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$7.71M</t>
+          <t>+$8.13M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>7452.4</v>
+        <v>7447.4</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7405</v>
+        <v>7400</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -577,31 +573,31 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$1.14M</t>
+          <t>-$18.27M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$1.57M</t>
+          <t>+$20.44M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7472.4</v>
+        <v>7452.4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7425</v>
+        <v>7405</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -610,86 +606,86 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$8.24M</t>
+          <t>-$2.90M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$9.36M</t>
+          <t>+$3.98M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>7457.4</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>-$7.24M</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>+$7.91M</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>7473.87</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>740</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>-$21.25M</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>+$25.54M</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>7483.91</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>741</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>-$6.87M</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>7462.4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7415</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-$3.76M</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+$4.18M</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -697,10 +693,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7492.4</v>
+        <v>7472.4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7445</v>
+        <v>7425</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -709,86 +705,86 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-$3.66M</t>
+          <t>-$16.24M</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+$4.60M</t>
+          <t>+$18.43M</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7473.87</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>-$21.25M</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>+$25.54M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7482.4</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>7435</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-$6.34M</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+$7.58M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7497.4</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>7450</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>-$13.78M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+$18.53M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>7517.4</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>7470</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>-$2.88M</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>+$8.12M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -796,291 +792,456 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7522.4</v>
+        <v>7483.91</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7475</v>
+        <v>741</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>-$6.87M</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7487.4</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7440</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-$10.89M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$19.76M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-$10.16M</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>+$11.24M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>7524.05</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>745</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>-$44.32M</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>+$82.47M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>7492.4</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7445</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>-$5.08M</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+$6.38M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>7497.4</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7450</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>-$17.43M</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+$23.42M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>7544.12</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>747</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>-$15.83M</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+$99.04M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>7547.4</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7517.4</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7470</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>+$5.34M</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$42.02M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-$2.40M</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$6.77M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>7552.4</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7505</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>-$3.02M</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+$13.21M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>7564.2</v>
+        <v>7522.4</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>749</v>
+        <v>7475</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$8.31M</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+$15.08M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>7524.05</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>745</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+$22.31M</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>+$123.96M</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>-$44.32M</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>+$82.47M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>7544.12</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>-$15.83M</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>+$99.04M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7572.4</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>7525</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$14.01M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>+$22.50M</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>7574.23</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>+$45.67M</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+$110.03M</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
+        <v>7547.4</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+$2.40M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+$18.89M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>7552.4</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>7505</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-$1.24M</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>+$5.40M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>7564.2</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>+$22.31M</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>+$123.96M</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>7572.4</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>7525</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>+$4.22M</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>+$6.78M</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7574.23</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>+$45.67M</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>+$110.03M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>7597.4</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B23" s="2" t="n">
         <v>7550</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>+$7.08M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$19.72M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>+$1.86M</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>+$5.19M</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1142,261 +1303,261 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>28386.9</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>685</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$2.68M</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$2.71M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>28592.5</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>690</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$3.62M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>28798.11</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>695</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$8.28M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$8.39M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>28839.23</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>696</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$1.42M</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>29003.72</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>-$11.67M</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$14.51M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>29085.97</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>702</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$6.61M</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$8.03M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>29168.21</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>704</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$3.52M</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$4.40M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>29168.48</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>28950</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>-$30.34K</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$30.34K</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>29208.48</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="2" t="n">
         <v>28990</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1406,125 +1567,125 @@
           <t>+$14.00K</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+$32.67K</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>29209.33</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>705</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$18.88M</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>29218.48</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>29000</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>-$123.40K</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>+$144.41K</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="2" t="n">
         <v>29248.48</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>29030</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>-$5.25K</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>+$73.52K</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="2" t="n">
         <v>29268.48</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>29050</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1534,96 +1695,96 @@
           <t>+$23.63K</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+$49.89K</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>29278.48</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>29060</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>-$65.64K</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>+$81.39K</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>29288.48</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>29070</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>-$2.63K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$13.13K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="2" t="n">
         <v>29291.57</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="2" t="n">
         <v>707</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1633,59 +1794,59 @@
           <t>+$1.41M</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>+$20.36M</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>29298.48</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="5" t="n">
         <v>29080</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>-$91.90K</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>+$91.90K</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="2" t="n">
         <v>29328.48</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="2" t="n">
         <v>29110</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1695,92 +1856,92 @@
           <t>$0</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+$11.67K</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="2" t="n">
         <v>29358.48</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="2" t="n">
         <v>29140</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>+$87.52K</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="2" t="n">
         <v>29368.48</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="2" t="n">
         <v>29150</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>-$55.43K</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>+$189.62K</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>29388.48</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>29170</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1790,30 +1951,30 @@
           <t>+$72.93K</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>+$84.60K</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="2" t="n">
         <v>29414.94</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="2" t="n">
         <v>710</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1823,59 +1984,59 @@
           <t>+$3.19M</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>+$27.76M</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>29418.48</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="5" t="n">
         <v>29200</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>+$175.04K</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="2" t="n">
         <v>29428.48</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="2" t="n">
         <v>29210</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1885,63 +2046,63 @@
           <t>+$5.83K</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>+$29.17K</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>29468.48</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="5" t="n">
         <v>29250</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>-$49.59K</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="2" t="n">
         <v>29497.18</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="2" t="n">
         <v>712</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -1951,26 +2112,26 @@
           <t>+$4.78M</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>+$15.72M</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="2" t="n">
         <v>29498.48</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="2" t="n">
         <v>29280</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1980,63 +2141,63 @@
           <t>+$2.92K</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>+$32.09K</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>29508.48</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="5" t="n">
         <v>29290</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>-$75.85K</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>+$169.20K</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="2" t="n">
         <v>29518.48</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="2" t="n">
         <v>29300</v>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -2046,63 +2207,63 @@
           <t>+$20.42K</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>+$107.94K</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="5" t="n">
         <v>29528.48</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="5" t="n">
         <v>29310</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>-$78.77K</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>+$125.44K</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="5" t="n">
         <v>29558.48</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="5" t="n">
         <v>29340</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -2112,92 +2273,92 @@
           <t>+$43.76K</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="2" t="n">
         <v>29588.48</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="2" t="n">
         <v>29370</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>-$10.50K</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>+$110.27K</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="2" t="n">
         <v>29598.48</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="2" t="n">
         <v>29380</v>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>-$36.76K</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="2" t="n">
         <v>29618.48</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="2" t="n">
         <v>29400</v>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -2207,26 +2368,26 @@
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>+$115.53K</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="5" t="n">
         <v>29620.55</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="5" t="n">
         <v>715</v>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2236,30 +2397,30 @@
           <t>+$16.34M</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>+$23.12M</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="2" t="n">
         <v>29785.04</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="2" t="n">
         <v>719</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2269,30 +2430,30 @@
           <t>+$1.25M</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>+$3.78M</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="5" t="n">
         <v>29826.16</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2302,30 +2463,30 @@
           <t>+$10.07M</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>+$13.32M</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="2" t="n">
         <v>30031.77</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="2" t="n">
         <v>725</v>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2335,17 +2496,17 @@
           <t>+$3.05M</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>+$7.40M</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G39"/>
@@ -2410,112 +2571,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>2927.46</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>291</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$9.47M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$9.54M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>2957.64</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>294</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$1.16M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$1.31M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>2967.7</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>295</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$5.60M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$6.17M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>2977.76</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>296</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
@@ -2525,92 +2686,92 @@
           <t>+$196.30K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$3.68M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>2987.82</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>297</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$2.86M</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$4.20M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>2997.88</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>298</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$548.37K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$5.75M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>3018</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
@@ -2620,17 +2781,17 @@
           <t>+$1.79M</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$3.62M</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -2699,13 +2860,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>67.16</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2715,30 +2876,30 @@
           <t>+$336.05K</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$635.04K</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>67.81</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2748,59 +2909,59 @@
           <t>+$195.51K</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$729.22K</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$81.55K</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$534.85K</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>70.39</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2810,30 +2971,30 @@
           <t>+$1.52M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$1.55M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>77.5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2843,17 +3004,17 @@
           <t>+$132.81K</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$132.81K</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G6"/>
@@ -2918,162 +3079,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>3909.4</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$2.16M</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$2.18M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>4011.38</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>363</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$218.51K</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$220.85K</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>4033.48</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$307.15K</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$346.02K</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4088.73</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$207.67K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$707.05K</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>4129.65</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>-$3.53M</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$3.90M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>4143.98</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3083,63 +3244,63 @@
           <t>+$320.55K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$1.52M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>4155.03</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>376</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>-$1.50M</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$2.03M</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>4199.24</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3149,26 +3310,26 @@
           <t>+$601.96K</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$1.82M</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>4254.49</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>385</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3178,30 +3339,30 @@
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$1.56M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>4349.9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3211,30 +3372,30 @@
           <t>+$16.71M</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$17.17M</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>4487.56</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>81.5</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3244,30 +3405,30 @@
           <t>+$32.65K</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$39.40K</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>4515.09</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3277,17 +3438,17 @@
           <t>+$7.65M</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>+$7.72M</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3306,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3362,18 +3523,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>7564.2</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>749</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3383,31 +3544,31 @@
           <t>+$22.31M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>+$123.96M</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>7574.23</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3417,89 +3578,89 @@
           <t>+$45.67M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>+$110.03M</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>7544.12</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>747</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>-$15.83M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>+$99.04M</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>7524.05</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5" t="n">
         <v>745</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>-$44.32M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>+$82.47M</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -3508,514 +3669,518 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7547.4</v>
+        <v>29414.94</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7500</v>
+        <v>710</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>+$5.34M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>+$3.19M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>+$42.02M</t>
+          <t>+$27.76M</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7473.87</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>-$21.25M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>+$25.54M</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>7497.4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7450</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-$17.43M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>+$23.42M</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>29414.94</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>710</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="B9" s="5" t="n">
+        <v>29620.55</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>715</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>+$3.19M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>+$27.76M</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>+$16.34M</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>+$23.12M</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7447.4</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7400</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-$18.27M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>+$20.44M</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>29291.57</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>707</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>+$1.41M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>+$20.36M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>7473.87</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>740</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-$21.25M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>+$25.54M</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="B12" s="5" t="n">
+        <v>7547.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>+$2.40M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+$18.89M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>29620.55</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>715</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>+$16.34M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>+$23.12M</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>7572.4</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>7525</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>+$14.01M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>+$22.50M</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>29291.57</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>707</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>+$1.41M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>+$20.36M</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>7522.4</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>7475</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-$10.89M</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>+$19.76M</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>29209.33</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>705</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-$10.38M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+$18.88M</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>7597.4</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>7550</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="B14" s="5" t="n">
+        <v>7472.4</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>+$7.08M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+$19.72M</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>29209.33</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>705</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-$10.38M</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>+$18.88M</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>-$16.24M</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+$18.43M</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>7497.4</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>7450</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-$13.78M</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>+$18.53M</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4349.9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>+$16.71M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>+$17.17M</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4349.9</v>
+        <v>29497.18</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>79</v>
+        <v>712</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>+$16.71M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>+$4.78M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+$17.17M</t>
+          <t>+$15.72M</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7522.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7475</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>-$8.31M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+$15.08M</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>29497.18</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>712</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="B18" s="5" t="n">
+        <v>29003.72</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>+$4.78M</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+$15.72M</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-$11.67M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>+$14.51M</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>29003.72</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B19" s="5" t="n">
+        <v>29826.16</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-$11.67M</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>+$14.51M</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>+$10.07M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>+$13.32M</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>29826.16</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>+$10.07M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>+$13.32M</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4028,10 +4193,10 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>7552.4</v>
+        <v>7487.4</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>7505</v>
+        <v>7440</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
@@ -4040,134 +4205,134 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-$3.02M</t>
+          <t>-$10.16M</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>+$13.21M</t>
+          <t>+$11.24M</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>7483.91</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-$6.87M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2927.46</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-$9.47M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>+$9.54M</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>7483.91</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>741</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>-$6.87M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>2927.46</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>291</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>-$9.47M</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>+$9.54M</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>28798.11</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>695</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>-$8.28M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+$8.39M</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>7472.4</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>7425</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>-$8.24M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>+$9.36M</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4176,126 +4341,122 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7437.4</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>7390</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>-$7.78M</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>+$8.13M</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>28798.11</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>695</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="B25" s="2" t="n">
+        <v>29085.97</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>-$8.28M</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>+$8.39M</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>7517.4</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>7470</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>-$2.88M</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>+$8.12M</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-$6.61M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>+$8.03M</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>29085.97</v>
+        <v>7457.4</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>702</v>
+        <v>7410</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>-$6.61M</t>
+          <t>-$7.24M</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>+$8.03M</t>
+          <t>+$7.91M</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="5" t="n">
         <v>4515.09</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -4305,17 +4466,17 @@
           <t>+$7.65M</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>+$7.72M</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4328,10 +4489,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7447.4</v>
+        <v>7482.4</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7400</v>
+        <v>7435</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -4340,164 +4501,168 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>-$6.89M</t>
+          <t>-$6.34M</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>+$7.71M</t>
+          <t>+$7.58M</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>30031.77</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>+$3.05M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+$7.40M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7572.4</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>7525</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>+$4.22M</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>+$6.78M</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>30031.77</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>725</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>+$3.05M</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>+$7.40M</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>2967.7</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>-$5.60M</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>+$6.17M</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>2997.88</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>-$548.37K</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>+$5.75M</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>7517.4</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7470</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>-$2.40M</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>+$6.77M</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="2" t="n">
         <v>7492.4</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="2" t="n">
         <v>7445</v>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>-$3.66M</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>+$4.60M</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>-$5.08M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>+$6.38M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4506,109 +4671,105 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>29168.21</v>
+        <v>2967.7</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>704</v>
+        <v>295</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>-$3.52M</t>
+          <t>-$5.60M</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>+$4.40M</t>
+          <t>+$6.17M</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>2987.82</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="B34" s="2" t="n">
+        <v>2997.88</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>-$2.86M</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>+$4.20M</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>-$548.37K</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+$5.75M</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>4129.65</v>
+        <v>7552.4</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>75</v>
+        <v>7505</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>-$3.53M</t>
+          <t>-$1.24M</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>+$3.90M</t>
+          <t>+$5.40M</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -4618,145 +4779,145 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>7597.4</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>+$1.86M</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>+$5.19M</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>29785.04</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>719</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>29168.21</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>+$1.25M</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>+$3.78M</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>-$3.52M</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>+$4.40M</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2987.82</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>-$2.86M</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>+$4.20M</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>28592.5</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>-$3.62M</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>+$3.70M</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>2977.76</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>296</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>+$196.30K</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>+$3.68M</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>3018</v>
+        <v>7462.4</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>300</v>
+        <v>7415</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>+$1.79M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-$3.76M</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>+$3.62M</t>
+          <t>+$4.18M</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -4766,38 +4927,42 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>28386.9</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>685</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>-$2.68M</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>+$2.71M</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>7452.4</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>7405</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>-$2.90M</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>+$3.98M</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -4806,10 +4971,10 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>3909.4</v>
+        <v>4129.65</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
@@ -4818,164 +4983,168 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>-$2.16M</t>
+          <t>-$3.53M</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>+$2.18M</t>
+          <t>+$3.90M</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4155.03</v>
+        <v>29785.04</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>376</v>
+        <v>719</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>-$1.50M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>+$1.25M</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>+$2.03M</t>
+          <t>+$3.78M</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>28592.5</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>-$3.62M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$3.70M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2977.76</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>+$196.30K</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>+$3.68M</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3018</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>+$1.79M</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>+$3.62M</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>4199.24</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>+$601.96K</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$1.82M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>7452.4</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>7405</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>-$1.14M</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>+$1.57M</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>4254.49</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>385</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>+$1.50M</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>+$1.56M</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4984,469 +5153,469 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>70.39</v>
+        <v>28386.9</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>109</v>
+        <v>685</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>+$1.52M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>-$2.68M</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>+$1.55M</t>
+          <t>+$2.71M</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>4143.98</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>+$320.55K</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>+$1.52M</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="B47" s="2" t="n">
+        <v>3909.4</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>-$2.16M</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>+$2.18M</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>28839.23</v>
+        <v>4155.03</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>696</v>
+        <v>376</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>-$1.42M</t>
+          <t>-$1.50M</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>+$1.50M</t>
+          <t>+$2.03M</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>2957.64</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-$1.16M</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>+$1.31M</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>4199.24</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>+$601.96K</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>+$1.82M</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>67.81</v>
+        <v>4254.49</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>105</v>
+        <v>385</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>+$195.51K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>+$1.50M</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>+$729.22K</t>
+          <t>+$1.56M</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>+$1.52M</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>+$1.55M</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B52" s="2" t="n">
+        <v>4143.98</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>+$320.55K</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$1.52M</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>28839.23</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>-$1.42M</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>+$1.50M</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2957.64</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>-$1.16M</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>+$1.31M</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>+$195.51K</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>+$729.22K</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>4088.73</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C56" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>-$207.67K</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>+$707.05K</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>+$336.05K</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$635.04K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-$81.55K</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>+$534.85K</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>4033.48</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>365</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>-$307.15K</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>+$346.02K</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>4011.38</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-$218.51K</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>+$220.85K</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>29368.48</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>29150</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-$55.43K</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>+$189.62K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>29418.48</v>
+        <v>67.16</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>29200</v>
+        <v>104</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>-$58.35K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>+$336.05K</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>+$175.04K</t>
+          <t>+$635.04K</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>29508.48</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>29290</v>
+        <v>107</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>-$75.85K</t>
+          <t>-$81.55K</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>+$169.20K</t>
+          <t>+$534.85K</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -5458,74 +5627,70 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>29218.48</v>
+        <v>4033.48</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>29000</v>
+        <v>365</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>-$123.40K</t>
+          <t>-$307.15K</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>+$144.41K</t>
+          <t>+$346.02K</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>4011.38</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>-$218.51K</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>+$220.85K</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -5534,10 +5699,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>29528.48</v>
+        <v>29368.48</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>29310</v>
+        <v>29150</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -5546,24 +5711,20 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>-$78.77K</t>
+          <t>-$55.43K</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>+$125.44K</t>
+          <t>+$189.62K</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5572,32 +5733,36 @@
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>29618.48</v>
+        <v>29418.48</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-$58.35K</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+$115.53K</t>
+          <t>+$175.04K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -5606,10 +5771,10 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>29588.48</v>
+        <v>29508.48</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>29370</v>
+        <v>29290</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
@@ -5618,20 +5783,24 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>-$10.50K</t>
+          <t>-$75.85K</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>+$110.27K</t>
+          <t>+$169.20K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -5640,110 +5809,106 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>29518.48</v>
+        <v>29218.48</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>29300</v>
+        <v>29000</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>+$20.42K</t>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-$123.40K</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>+$107.94K</t>
+          <t>+$144.41K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>+$132.81K</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>+$132.81K</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>29468.48</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>29250</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B66" s="5" t="n">
+        <v>29528.48</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>29310</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>-$49.59K</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>+$102.11K</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-$78.77K</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>+$125.44K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>29558.48</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>29340</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>+$43.76K</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>+$102.11K</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
@@ -5754,74 +5919,66 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>29298.48</v>
+        <v>29618.48</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>29080</v>
+        <v>29400</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-$91.90K</t>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>+$91.90K</t>
+          <t>+$115.53K</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
-        <v>29358.48</v>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>29140</v>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="B68" s="2" t="n">
+        <v>29588.48</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>29370</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-$58.35K</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>+$87.52K</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>-$10.50K</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>+$110.27K</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -5830,70 +5987,70 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>29388.48</v>
+        <v>29518.48</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>29170</v>
+        <v>29300</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>+$72.93K</t>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>+$20.42K</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>+$84.60K</t>
+          <t>+$107.94K</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>29468.48</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>29250</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-$49.59K</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>+$102.11K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>29278.48</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>29060</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>-$65.64K</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>+$81.39K</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -5906,32 +6063,36 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>29248.48</v>
+        <v>29558.48</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>29030</v>
+        <v>29340</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>-$5.25K</t>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>+$43.76K</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>+$73.52K</t>
+          <t>+$102.11K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -5940,70 +6101,70 @@
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>29268.48</v>
+        <v>29298.48</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>29050</v>
+        <v>29080</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>+$23.63K</t>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>-$91.90K</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>+$49.89K</t>
+          <t>+$91.90K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>29358.48</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>29140</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-$58.35K</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>+$87.52K</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="n">
-        <v>29598.48</v>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>29380</v>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>-$36.76K</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -6012,38 +6173,38 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>4487.56</v>
+        <v>29388.48</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>81.5</v>
+        <v>29170</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>+$32.65K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>+$72.93K</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>+$39.40K</t>
+          <t>+$84.60K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -6054,225 +6215,411 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
+        <v>29278.48</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>29060</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>-$65.64K</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>+$81.39K</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>29248.48</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>29030</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>-$5.25K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$73.52K</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>29268.48</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>29050</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>+$23.63K</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>+$49.89K</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>29598.48</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>29380</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>-$36.76K</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>4487.56</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>+$32.65K</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>+$39.40K</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
         <v>29208.48</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C80" s="2" t="n">
         <v>28990</v>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>+$14.00K</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>+$32.67K</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B81" s="2" t="n">
         <v>29498.48</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C81" s="2" t="n">
         <v>29280</v>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>+$2.92K</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>+$32.09K</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B82" s="2" t="n">
         <v>29168.48</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C82" s="2" t="n">
         <v>28950</v>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>-$30.34K</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>+$30.34K</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B83" s="2" t="n">
         <v>29428.48</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C83" s="2" t="n">
         <v>29210</v>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>+$5.83K</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>+$29.17K</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B84" s="2" t="n">
         <v>29288.48</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C84" s="2" t="n">
         <v>29070</v>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>-$2.63K</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>+$13.13K</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B85" s="2" t="n">
         <v>29328.48</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C85" s="2" t="n">
         <v>29110</v>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>+$11.67K</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H80"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gex_pivot_levels_2026-07-08.xlsx
+++ b/gex_pivot_levels_2026-07-08.xlsx
@@ -17,10 +17,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,6 +91,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -100,19 +109,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -544,27 +544,31 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$7.78M</t>
+          <t>-$8.45M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$8.13M</t>
+          <t>+$8.82M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>7447.4</v>
+        <v>7442.4</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7400</v>
+        <v>7395</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -573,31 +577,31 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$18.27M</t>
+          <t>-$4.95M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$20.44M</t>
+          <t>+$5.39M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7452.4</v>
+        <v>7447.4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7405</v>
+        <v>7400</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -606,31 +610,31 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$2.90M</t>
+          <t>-$19.65M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$3.98M</t>
+          <t>+$21.98M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>7457.4</v>
+        <v>7452.4</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7410</v>
+        <v>7405</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -639,31 +643,31 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$7.24M</t>
+          <t>-$3.05M</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$7.91M</t>
+          <t>+$4.20M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7462.4</v>
+        <v>7457.4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7415</v>
+        <v>7410</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -672,86 +676,86 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-$3.76M</t>
+          <t>-$7.61M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$4.18M</t>
+          <t>+$8.32M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
+        <v>7462.4</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7415</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-$3.89M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+$4.32M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>7472.4</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>7425</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$16.24M</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$18.43M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7473.87</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>740</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>-$21.25M</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>+$25.54M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -759,65 +763,65 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>7473.87</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-$21.25M</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+$25.54M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>7482.4</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>7435</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>-$6.34M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+$7.58M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-$6.25M</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>+$7.47M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>7483.91</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>741</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-$6.87M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -825,43 +829,43 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>7487.4</v>
+        <v>7483.91</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7440</v>
+        <v>741</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>-$10.16M</t>
+          <t>-$6.87M</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+$11.24M</t>
+          <t>+$10.10M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7492.4</v>
+        <v>7487.4</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7445</v>
+        <v>7440</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -870,31 +874,31 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-$5.08M</t>
+          <t>-$9.71M</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>+$6.38M</t>
+          <t>+$10.75M</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>7497.4</v>
+        <v>7492.4</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7450</v>
+        <v>7445</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -903,31 +907,31 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-$17.43M</t>
+          <t>-$4.78M</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+$23.42M</t>
+          <t>+$6.01M</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7517.4</v>
+        <v>7497.4</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7470</v>
+        <v>7450</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -936,86 +940,86 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-$2.40M</t>
+          <t>-$16.39M</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>+$6.77M</t>
+          <t>+$22.02M</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
+        <v>7517.4</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>7470</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$2.12M</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+$5.98M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
         <v>7522.4</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>7475</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>-$8.31M</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>+$15.08M</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-$7.16M</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+$13.00M</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>7524.05</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>745</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>-$44.32M</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>+$82.47M</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -1023,10 +1027,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7544.12</v>
+        <v>7524.05</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -1035,115 +1039,111 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>-$15.83M</t>
+          <t>-$44.32M</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>+$99.04M</t>
+          <t>+$82.47M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
+        <v>7544.12</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>747</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>-$15.83M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+$99.04M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
         <v>7547.4</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B19" s="5" t="n">
         <v>7500</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>+$2.40M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$18.89M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>7552.4</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>7505</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>-$1.24M</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>+$5.40M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>+$1.92M</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>+$15.11M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>7564.2</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="5" t="n">
         <v>749</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>+$22.31M</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>+$123.96M</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1159,86 +1159,82 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>+$4.22M</t>
+          <t>+$3.26M</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>+$6.78M</t>
+          <t>+$5.24M</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>7574.23</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>+$45.67M</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>+$110.03M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>7574.23</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>+$45.67M</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>+$110.03M</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>7597.4</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="5" t="n">
         <v>7550</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+$1.86M</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>+$1.49M</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>+$4.15M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G23"/>
@@ -1303,1210 +1299,1210 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>28386.9</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>685</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$2.68M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$2.71M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>28592.5</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>690</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>-$3.62M</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>28798.11</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>695</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$8.28M</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$8.39M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>28839.23</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>696</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>-$1.42M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>29003.72</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>700</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$11.67M</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$14.51M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>29085.97</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>702</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>-$6.61M</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>+$8.03M</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>29168.21</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>704</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>-$3.52M</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$4.40M</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>29168.48</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>28950</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>-$30.34K</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$30.34K</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>29208.48</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>28990</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+$14.00K</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$32.67K</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>29209.33</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="2" t="n">
         <v>705</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>+$18.88M</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>29218.48</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>29000</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>-$123.40K</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$144.41K</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>29248.48</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>29030</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>-$5.25K</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>+$73.52K</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>29268.48</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="5" t="n">
         <v>29050</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>+$23.63K</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>+$49.89K</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="2" t="n">
         <v>29278.48</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="2" t="n">
         <v>29060</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>-$65.64K</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>+$81.39K</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>29288.48</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="5" t="n">
         <v>29070</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>-$2.63K</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>+$13.13K</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>29291.57</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>707</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>+$1.41M</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+$20.36M</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="2" t="n">
         <v>29298.48</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="2" t="n">
         <v>29080</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>-$91.90K</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>+$91.90K</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>29328.48</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="5" t="n">
         <v>29110</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>+$11.67K</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>29358.48</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="5" t="n">
         <v>29140</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>+$87.52K</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>29368.48</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="5" t="n">
         <v>29150</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>-$55.43K</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>+$189.62K</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="2" t="n">
         <v>29388.48</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="2" t="n">
         <v>29170</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>+$72.93K</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>+$84.60K</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>29414.94</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>+$3.19M</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>+$27.76M</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="2" t="n">
         <v>29418.48</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="2" t="n">
         <v>29200</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>+$175.04K</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="5" t="n">
         <v>29428.48</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="5" t="n">
         <v>29210</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>+$5.83K</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>+$29.17K</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="2" t="n">
         <v>29468.48</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="2" t="n">
         <v>29250</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>-$49.59K</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>29497.18</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="5" t="n">
         <v>712</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>+$4.78M</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>+$15.72M</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="5" t="n">
         <v>29498.48</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="5" t="n">
         <v>29280</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>+$2.92K</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>+$32.09K</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="2" t="n">
         <v>29508.48</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="2" t="n">
         <v>29290</v>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>-$75.85K</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>+$169.20K</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="5" t="n">
         <v>29518.48</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>+$20.42K</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>+$107.94K</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="2" t="n">
         <v>29528.48</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="2" t="n">
         <v>29310</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>-$78.77K</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>+$125.44K</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="2" t="n">
         <v>29558.48</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="2" t="n">
         <v>29340</v>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>+$43.76K</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="5" t="n">
         <v>29588.48</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="5" t="n">
         <v>29370</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>-$10.50K</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>+$110.27K</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="5" t="n">
         <v>29598.48</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="5" t="n">
         <v>29380</v>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>-$36.76K</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>29618.48</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="5" t="n">
         <v>29400</v>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>+$115.53K</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="2" t="n">
         <v>29620.55</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="2" t="n">
         <v>715</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>+$16.34M</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>+$23.12M</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="5" t="n">
         <v>29785.04</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="5" t="n">
         <v>719</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>+$1.25M</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>+$3.78M</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="2" t="n">
         <v>29826.16</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="2" t="n">
         <v>720</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>+$10.07M</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>+$13.32M</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="5" t="n">
         <v>30031.77</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="5" t="n">
         <v>725</v>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>+$3.05M</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>+$7.40M</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G39"/>
@@ -2521,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2571,66 +2567,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>2927.46</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>291</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>-$9.47M</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>+$9.54M</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>-$9.77M</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+$9.84M</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2957.64</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>294</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>2937.52</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>-$1.16M</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>+$1.31M</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>-$2.46M</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>+$2.57M</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -2650,17 +2646,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>-$5.60M</t>
+          <t>-$8.94M</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>+$6.17M</t>
+          <t>+$10.72M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2670,135 +2666,69 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>2977.76</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>296</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>+$196.30K</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>+$3.68M</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>-$5.33M</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>+$14.36M</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2987.82</v>
+        <v>3018</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>-$2.86M</t>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>+$10.86M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$4.20M</t>
+          <t>+$12.98M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2997.88</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>-$548.37K</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+$5.75M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>3018</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>+$1.79M</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>+$3.62M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2860,106 +2790,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>+$336.05K</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>+$635.04K</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>-$418.52K</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>+$1.22M</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>+$195.51K</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>+$729.22K</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>+$445.61K</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>+$2.37M</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-$81.55K</t>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>+$3.85M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$534.85K</t>
+          <t>+$3.99M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>70.39</v>
+        <v>72.97</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -2968,53 +2898,49 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>+$1.52M</t>
+          <t>+$850.11K</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$1.55M</t>
+          <t>+$856.86K</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>+$500.56K</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>+$514.55K</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G6"/>
@@ -3079,376 +3005,376 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>3909.4</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$2.16M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$2.18M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>4011.38</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>363</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>-$218.51K</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>+$220.85K</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>4033.48</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$307.15K</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$346.02K</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>4088.73</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>-$207.67K</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$707.05K</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>4129.65</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$3.53M</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$3.90M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>4143.98</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>375</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>+$320.55K</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>+$1.52M</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>4155.03</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>376</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$1.50M</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$2.03M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>4199.24</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>380</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+$601.96K</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$1.82M</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>4254.49</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+$1.56M</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>4349.9</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>+$16.71M</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>+$17.17M</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>4487.56</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>81.5</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>+$32.65K</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>+$39.40K</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="2" t="n">
         <v>4515.09</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>+$7.65M</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>+$7.72M</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3467,7 +3393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3523,588 +3449,584 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>7564.2</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5" t="n">
         <v>749</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>+$22.31M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>+$123.96M</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>7574.23</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>+$45.67M</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>+$110.03M</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>7544.12</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5" t="n">
         <v>747</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>-$15.83M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>+$99.04M</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>7524.05</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>745</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>-$44.32M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>+$82.47M</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>29414.94</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>+$3.19M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>+$27.76M</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>7473.87</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>740</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-$21.25M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>+$25.54M</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>29620.55</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>+$16.34M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+$23.12M</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>7497.4</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C9" s="2" t="n">
         <v>7450</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>-$17.43M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>+$23.42M</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-$16.39M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>+$22.02M</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>7447.4</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7400</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-$19.65M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>+$21.98M</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>29620.55</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>715</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="B11" s="5" t="n">
+        <v>29291.57</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>707</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>+$16.34M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>+$23.12M</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>+$1.41M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>+$20.36M</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>29209.33</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-$10.38M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>+$18.88M</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>7472.4</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-$16.24M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>+$18.43M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4349.9</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>+$16.71M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+$17.17M</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>7447.4</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>7400</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>-$18.27M</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>+$20.44M</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>29291.57</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>707</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>+$1.41M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>+$20.36M</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>7547.4</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>+$2.40M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+$18.89M</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>29209.33</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>705</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>-$10.38M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+$18.88M</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7472.4</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>7425</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>-$16.24M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+$18.43M</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4349.9</v>
+        <v>29497.18</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>79</v>
+        <v>712</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>+$16.71M</t>
+          <t>+$4.78M</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>+$17.17M</t>
+          <t>+$15.72M</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7547.4</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>+$1.92M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>+$15.11M</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>29003.72</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-$11.67M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>+$14.51M</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>29497.18</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>712</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>+$4.78M</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>+$15.72M</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>7522.4</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>7475</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>-$8.31M</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+$15.08M</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4113,112 +4035,108 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2977.76</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-$5.33M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>+$14.36M</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>29003.72</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="B19" s="2" t="n">
+        <v>29826.16</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>-$11.67M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>+$14.51M</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>+$10.07M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+$13.32M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>29826.16</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>+$10.07M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>+$13.32M</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>7522.4</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>7475</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-$7.16M</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>+$13.00M</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>7487.4</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>7440</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>-$10.16M</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>+$11.24M</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4227,74 +4145,74 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3018</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>+$10.86M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$12.98M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>7483.91</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>741</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>-$6.87M</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2927.46</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>291</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>-$9.47M</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>+$9.54M</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="B22" s="2" t="n">
+        <v>7487.4</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>7440</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>-$9.71M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>+$10.75M</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4303,33 +4221,33 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>28798.11</v>
+        <v>2967.7</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>695</v>
+        <v>295</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>-$8.28M</t>
+          <t>-$8.94M</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>+$8.39M</t>
+          <t>+$10.72M</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -4339,146 +4257,154 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>7437.4</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>7390</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>-$7.78M</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>+$8.13M</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="B24" s="5" t="n">
+        <v>7483.91</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>741</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-$6.87M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2927.46</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-$9.77M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>+$9.84M</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7437.4</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>7390</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>-$8.45M</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>+$8.82M</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>29085.97</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>702</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="B27" s="2" t="n">
+        <v>28798.11</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-$6.61M</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>+$8.03M</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>7457.4</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>7410</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>-$7.24M</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>+$7.91M</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>-$8.28M</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>+$8.39M</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>4515.09</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>+$7.65M</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>+$7.72M</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4489,734 +4415,730 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
+        <v>7457.4</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>7410</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>-$7.61M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+$8.32M</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>29085.97</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>702</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>-$6.61M</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>+$8.03M</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>4515.09</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>+$7.65M</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>+$7.72M</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
         <v>7482.4</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C31" s="5" t="n">
         <v>7435</v>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>-$6.34M</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>+$7.58M</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>-$6.25M</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>+$7.47M</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B32" s="5" t="n">
         <v>30031.77</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C32" s="5" t="n">
         <v>725</v>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>+$3.05M</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>+$7.40M</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>7572.4</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>7525</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>+$4.22M</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>+$6.78M</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>7517.4</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>7470</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>-$2.40M</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>+$6.77M</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>7492.4</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>7445</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>-$5.08M</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>+$6.38M</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2967.7</v>
+        <v>7492.4</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>295</v>
+        <v>7445</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>-$5.60M</t>
+          <t>-$4.78M</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>+$6.17M</t>
+          <t>+$6.01M</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>7517.4</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>7470</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>-$2.12M</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>+$5.98M</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>7442.4</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>7395</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>-$4.95M</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>+$5.39M</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>7572.4</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>7525</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>+$3.26M</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>+$5.24M</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>29168.21</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>704</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>-$3.52M</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>+$4.40M</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>7462.4</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>7415</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>-$3.89M</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>+$4.32M</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>7452.4</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>7405</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>-$3.05M</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>+$4.20M</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>7597.4</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>+$1.49M</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>+$4.15M</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>+$3.85M</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>+$3.99M</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>2997.88</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>-$548.37K</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>+$5.75M</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>7552.4</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>7505</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>-$1.24M</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>+$5.40M</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>7597.4</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>7550</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>+$1.86M</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>29168.21</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>-$3.52M</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>+$4.40M</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>2987.82</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>-$2.86M</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>+$4.20M</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>7462.4</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>7415</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>-$3.76M</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>+$4.18M</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>7452.4</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>7405</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>-$2.90M</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>+$3.98M</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>4129.65</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>-$3.53M</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>+$3.90M</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>4129.65</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>-$3.53M</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>+$3.90M</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B43" s="5" t="n">
         <v>29785.04</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C43" s="5" t="n">
         <v>719</v>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>+$1.25M</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>+$3.78M</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B44" s="5" t="n">
         <v>28592.5</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C44" s="5" t="n">
         <v>690</v>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>-$3.62M</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>2977.76</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>+$196.30K</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>+$3.68M</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>28386.9</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>685</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-$2.68M</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>+$2.71M</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>3018</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="B46" s="5" t="n">
+        <v>2937.52</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>+$1.79M</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>+$3.62M</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>-$2.46M</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>+$2.57M</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>28386.9</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>685</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>-$2.68M</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>+$2.71M</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>+$445.61K</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>+$2.37M</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>3909.4</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>-$2.16M</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>+$2.18M</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -5225,36 +5147,32 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>4155.03</v>
+        <v>3909.4</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>376</v>
+        <v>71</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>-$1.50M</t>
+          <t>-$2.16M</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>+$2.03M</t>
+          <t>+$2.18M</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -5263,32 +5181,36 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4199.24</v>
+        <v>4155.03</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>+$601.96K</t>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>-$1.50M</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>+$1.82M</t>
+          <t>+$2.03M</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -5297,400 +5219,388 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
+        <v>4199.24</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>380</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>+$601.96K</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>+$1.82M</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>4254.49</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C51" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>+$1.56M</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>4143.98</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>+$320.55K</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>+$1.52M</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>28839.23</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>696</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>-$1.42M</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>+$1.50M</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="B54" s="5" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>+$1.52M</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>+$1.55M</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>-$418.52K</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>+$1.22M</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>+$850.11K</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>+$856.86K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>4143.98</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>375</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="B56" s="5" t="n">
+        <v>4088.73</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>+$320.55K</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>+$1.52M</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>-$207.67K</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>+$707.05K</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>+$500.56K</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>+$514.55K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4033.48</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>365</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-$307.15K</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>+$346.02K</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>4011.38</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-$218.51K</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>+$220.85K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>28839.23</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>696</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>-$1.42M</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>+$1.50M</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>2957.64</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>294</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>-$1.16M</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>+$1.31M</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>+$195.51K</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>+$729.22K</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="B60" s="5" t="n">
+        <v>29368.48</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>29150</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>-$55.43K</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>+$189.62K</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>4088.73</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>370</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>-$207.67K</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>+$707.05K</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>+$336.05K</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>+$635.04K</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>-$81.55K</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>+$534.85K</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>4033.48</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>-$307.15K</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>+$346.02K</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>4011.38</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>363</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>-$218.51K</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>+$220.85K</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -5699,10 +5609,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>29368.48</v>
+        <v>29418.48</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>29150</v>
+        <v>29200</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -5711,168 +5621,172 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>-$55.43K</t>
+          <t>-$58.35K</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>+$189.62K</t>
+          <t>+$175.04K</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>29508.48</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>29290</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>-$75.85K</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>+$169.20K</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>29218.48</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>-$123.40K</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>+$144.41K</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>29528.48</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>29310</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>-$78.77K</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>+$125.44K</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>29618.48</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>29400</v>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>+$115.53K</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>29418.48</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>29200</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>-$58.35K</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>+$175.04K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>29508.48</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>29290</v>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-$75.85K</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>+$169.20K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>29218.48</v>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-$123.40K</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>+$144.41K</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>+$132.81K</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -5881,10 +5795,10 @@
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>29528.48</v>
+        <v>29588.48</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>29310</v>
+        <v>29370</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
@@ -5893,58 +5807,58 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-$78.77K</t>
+          <t>-$10.50K</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>+$125.44K</t>
+          <t>+$110.27K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>29618.48</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>29400</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="5" t="n">
+        <v>29518.48</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>29300</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>+$115.53K</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>+$20.42K</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>+$107.94K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -5953,10 +5867,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>29588.48</v>
+        <v>29468.48</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>29370</v>
+        <v>29250</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -5965,20 +5879,24 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>-$10.50K</t>
+          <t>-$49.59K</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>+$110.27K</t>
+          <t>+$102.11K</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -5987,10 +5905,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>29518.48</v>
+        <v>29558.48</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>29300</v>
+        <v>29340</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -5999,17 +5917,17 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>+$20.42K</t>
+          <t>+$43.76K</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>+$107.94K</t>
+          <t>+$102.11K</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -6019,38 +5937,38 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n">
-        <v>29468.48</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>29250</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="B70" s="2" t="n">
+        <v>29298.48</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>29080</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-$49.59K</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>+$102.11K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>-$91.90K</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>+$91.90K</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -6063,72 +5981,72 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>29558.48</v>
+        <v>29358.48</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>29340</v>
+        <v>29140</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>+$43.76K</t>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>-$58.35K</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>+$102.11K</t>
+          <t>+$87.52K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>29388.48</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>29170</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>+$72.93K</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>+$84.60K</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>29298.48</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>29080</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>-$91.90K</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>+$91.90K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
@@ -6139,10 +6057,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>29358.48</v>
+        <v>29278.48</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>29140</v>
+        <v>29060</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -6151,17 +6069,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>-$58.35K</t>
+          <t>-$65.64K</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>+$87.52K</t>
+          <t>+$81.39K</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -6177,36 +6095,32 @@
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>29388.48</v>
+        <v>29248.48</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>29170</v>
+        <v>29030</v>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>+$72.93K</t>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>-$5.25K</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>+$84.60K</t>
+          <t>+$73.52K</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -6215,411 +6129,339 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>29278.48</v>
+        <v>29268.48</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>29060</v>
+        <v>29050</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-$65.64K</t>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>+$23.63K</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>+$81.39K</t>
+          <t>+$49.89K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>29598.48</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>29380</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-$36.76K</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>4487.56</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>+$32.65K</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>+$39.40K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
-        <v>29248.48</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>29030</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B78" s="5" t="n">
+        <v>29208.48</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>28990</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>-$5.25K</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>+$73.52K</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>+$14.00K</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>+$32.67K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>29498.48</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>29280</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>+$2.92K</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>+$32.09K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>29168.48</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>28950</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-$30.34K</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>+$30.34K</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>29268.48</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>29050</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B81" s="5" t="n">
+        <v>29428.48</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>29210</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>+$23.63K</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>+$49.89K</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>+$5.83K</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>+$29.17K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
-        <v>29598.48</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>29380</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B82" s="5" t="n">
+        <v>29288.48</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>29070</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>-$36.76K</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>-$2.63K</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>+$13.13K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>4487.56</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>+$32.65K</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>+$39.40K</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>29328.48</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>29110</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>+$11.67K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>29208.48</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>28990</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>+$14.00K</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>+$32.67K</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>29498.48</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>29280</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>+$2.92K</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>+$32.09K</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>29168.48</v>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>28950</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>-$30.34K</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>+$30.34K</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>29428.48</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>29210</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>+$5.83K</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>+$29.17K</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n">
-        <v>29288.48</v>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>29070</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>-$2.63K</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>+$13.13K</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>29328.48</v>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>29110</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>+$11.67K</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:H83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gex_pivot_levels_2026-07-08.xlsx
+++ b/gex_pivot_levels_2026-07-08.xlsx
@@ -91,6 +91,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -100,19 +109,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -544,31 +544,27 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$8.45M</t>
+          <t>-$7.78M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$8.82M</t>
+          <t>+$8.13M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>7442.4</v>
+        <v>7447.4</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7395</v>
+        <v>7400</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -577,31 +573,31 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$4.95M</t>
+          <t>-$18.62M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$5.39M</t>
+          <t>+$20.83M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7447.4</v>
+        <v>7452.4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7400</v>
+        <v>7405</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -610,31 +606,31 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$19.65M</t>
+          <t>-$3.00M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$21.98M</t>
+          <t>+$4.13M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>7452.4</v>
+        <v>7457.4</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7405</v>
+        <v>7410</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -643,31 +639,31 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$3.05M</t>
+          <t>-$7.61M</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$4.20M</t>
+          <t>+$8.32M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7457.4</v>
+        <v>7462.4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7410</v>
+        <v>7415</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -676,31 +672,31 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-$7.61M</t>
+          <t>-$3.95M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$8.32M</t>
+          <t>+$4.39M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7462.4</v>
+        <v>7472.4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7415</v>
+        <v>7425</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -709,53 +705,53 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-$3.89M</t>
+          <t>-$17.24M</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+$4.32M</t>
+          <t>+$19.57M</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7472.4</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>7425</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>-$16.24M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+$18.43M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="n">
+        <v>7473.87</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>-$21.25M</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>+$25.54M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -763,65 +759,65 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7473.87</v>
+        <v>7482.4</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>740</v>
+        <v>7435</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-$6.82M</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+$8.15M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>7483.91</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>-$21.25M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+$25.54M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>7482.4</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>7435</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>-$6.25M</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>+$7.47M</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>-$6.87M</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -829,43 +825,43 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>7483.91</v>
+        <v>7487.4</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>741</v>
+        <v>7440</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>-$6.87M</t>
+          <t>-$10.91M</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+$10.10M</t>
+          <t>+$12.07M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7487.4</v>
+        <v>7492.4</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7440</v>
+        <v>7445</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -874,31 +870,31 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-$9.71M</t>
+          <t>-$5.45M</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>+$10.75M</t>
+          <t>+$6.85M</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>7492.4</v>
+        <v>7497.4</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>7445</v>
+        <v>7450</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -907,31 +903,31 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-$4.78M</t>
+          <t>-$18.99M</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+$6.01M</t>
+          <t>+$25.52M</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7497.4</v>
+        <v>7517.4</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7450</v>
+        <v>7470</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -940,31 +936,31 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-$16.39M</t>
+          <t>-$2.60M</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>+$22.02M</t>
+          <t>+$7.33M</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>7517.4</v>
+        <v>7522.4</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>7470</v>
+        <v>7475</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -973,53 +969,53 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>-$2.12M</t>
+          <t>-$8.74M</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>+$5.98M</t>
+          <t>+$15.86M</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7522.4</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>7475</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>-$7.16M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>+$13.00M</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>7524.05</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>745</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>-$44.32M</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>+$82.47M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -1027,10 +1023,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7524.05</v>
+        <v>7544.12</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -1039,111 +1035,115 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>-$44.32M</t>
+          <t>-$15.83M</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>+$82.47M</t>
+          <t>+$99.04M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>7544.12</v>
+        <v>7547.4</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>747</v>
+        <v>7500</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+$2.34M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+$18.41M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>7552.4</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>7505</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-$1.20M</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>+$5.25M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>7564.2</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>-$15.83M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$99.04M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>+$22.31M</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>+$123.96M</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>7547.4</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>+$1.92M</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>+$15.11M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>7564.2</v>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>749</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>+$22.31M</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>+$123.96M</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1159,82 +1159,86 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>+$3.26M</t>
+          <t>+$3.84M</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>+$5.24M</t>
+          <t>+$6.16M</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7574.23</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>+$45.67M</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>+$110.03M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>7597.4</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>7550</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>+$1.49M</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>+$4.15M</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>7574.23</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+$45.67M</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>+$110.03M</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>7597.4</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>7550</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>+$1.49M</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>+$4.15M</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G23"/>
@@ -1299,1210 +1303,1210 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>28386.9</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>685</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$2.68M</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$2.71M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>28592.5</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>690</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$3.62M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>28798.11</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>695</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$8.28M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$8.39M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>28839.23</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>696</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$1.42M</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$1.50M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>29003.72</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>-$11.67M</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$14.51M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>29085.97</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>702</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$6.61M</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$8.03M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>29168.21</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>704</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$3.52M</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$4.40M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>29168.48</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>28950</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>-$30.34K</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$30.34K</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>29208.48</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="2" t="n">
         <v>28990</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>+$14.00K</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+$32.67K</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>29209.33</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>705</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$18.88M</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>29218.48</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>29000</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>-$123.40K</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>+$144.41K</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="2" t="n">
         <v>29248.48</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>29030</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>-$5.25K</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>+$73.52K</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="2" t="n">
         <v>29268.48</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>29050</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>+$23.63K</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+$49.89K</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>29278.48</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="5" t="n">
         <v>29060</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>-$65.64K</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>+$81.39K</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>29288.48</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>29070</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>-$2.63K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$13.13K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="2" t="n">
         <v>29291.57</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="2" t="n">
         <v>707</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>+$1.41M</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>+$20.36M</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>29298.48</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="5" t="n">
         <v>29080</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>-$91.90K</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>+$91.90K</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="2" t="n">
         <v>29328.48</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="2" t="n">
         <v>29110</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+$11.67K</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="2" t="n">
         <v>29358.48</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="2" t="n">
         <v>29140</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>+$87.52K</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="2" t="n">
         <v>29368.48</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="2" t="n">
         <v>29150</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>-$55.43K</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>+$189.62K</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>29388.48</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>29170</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>+$72.93K</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>+$84.60K</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="2" t="n">
         <v>29414.94</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="2" t="n">
         <v>710</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>+$3.19M</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>+$27.76M</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>29418.48</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="5" t="n">
         <v>29200</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>-$58.35K</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>+$175.04K</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="2" t="n">
         <v>29428.48</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="2" t="n">
         <v>29210</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>+$5.83K</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>+$29.17K</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>29468.48</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="5" t="n">
         <v>29250</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>-$49.59K</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="2" t="n">
         <v>29497.18</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="2" t="n">
         <v>712</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>+$4.78M</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>+$15.72M</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="2" t="n">
         <v>29498.48</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="2" t="n">
         <v>29280</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>+$2.92K</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>+$32.09K</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>29508.48</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="5" t="n">
         <v>29290</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>-$75.85K</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>+$169.20K</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="2" t="n">
         <v>29518.48</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="2" t="n">
         <v>29300</v>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>+$20.42K</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>+$107.94K</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="5" t="n">
         <v>29528.48</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="5" t="n">
         <v>29310</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>-$78.77K</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>+$125.44K</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="5" t="n">
         <v>29558.48</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="5" t="n">
         <v>29340</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>+$43.76K</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>+$102.11K</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="2" t="n">
         <v>29588.48</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="2" t="n">
         <v>29370</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>-$10.50K</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>+$110.27K</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="2" t="n">
         <v>29598.48</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="2" t="n">
         <v>29380</v>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>-$36.76K</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="2" t="n">
         <v>29618.48</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="2" t="n">
         <v>29400</v>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>+$42.01K</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>+$115.53K</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="5" t="n">
         <v>29620.55</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="5" t="n">
         <v>715</v>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>+$16.34M</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>+$23.12M</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="2" t="n">
         <v>29785.04</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="2" t="n">
         <v>719</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>+$1.25M</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>+$3.78M</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="5" t="n">
         <v>29826.16</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>+$10.07M</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>+$13.32M</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="2" t="n">
         <v>30031.77</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="2" t="n">
         <v>725</v>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>+$3.05M</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>+$7.40M</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G39"/>
@@ -2567,161 +2571,161 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>2927.46</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>291</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$9.77M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$9.84M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>2937.52</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>292</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$2.46M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$2.57M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>2967.7</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>295</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$8.94M</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$10.72M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>2977.76</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>296</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$5.33M</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$14.36M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>3018</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>+$10.86M</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$12.98M</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -2790,157 +2794,157 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$418.52K</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$1.22M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>69.75</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>+$445.61K</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$2.37M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>71.04000000000001</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>+$3.85M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$3.99M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>72.97</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>+$850.11K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$856.86K</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>74.27</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>+$500.56K</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$514.55K</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G6"/>
@@ -3005,98 +3009,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>3909.4</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$2.16M</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$2.18M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>4011.38</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>4088.73</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>-$218.51K</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>+$220.85K</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>-$371.00K</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+$893.93K</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>4033.48</v>
+        <v>4129.65</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>-$307.15K</t>
+          <t>-$3.88M</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>+$346.02K</t>
+          <t>+$4.26M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>4088.73</v>
+        <v>4155.03</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -3105,117 +3113,121 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$207.67K</t>
+          <t>-$3.54M</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$707.05K</t>
+          <t>+$4.17M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4129.65</v>
+        <v>4166.09</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>75</v>
+        <v>377</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-$3.53M</t>
+          <t>-$151.57K</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$3.90M</t>
+          <t>+$1.14M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4143.98</v>
+        <v>4177.14</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+$320.55K</t>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-$2.10M</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+$1.52M</t>
+          <t>+$3.25M</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4155.03</v>
+        <v>4188.19</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>-$1.50M</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>+$416.45K</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$2.03M</t>
+          <t>+$1.21M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -3231,150 +3243,154 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>+$601.96K</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>-$1.44M</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>+$1.82M</t>
+          <t>+$5.36M</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>4254.49</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>385</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>+$1.50M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$1.56M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>+$1.86M</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>+$1.91M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>4349.9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>+$16.71M</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>+$17.17M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>+$17.36M</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>+$17.81M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>4487.56</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>81.5</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>+$32.65K</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+$39.40K</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>+$42.62K</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+$49.35K</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>4515.09</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>+$7.65M</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$7.72M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>+$7.61M</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+$7.68M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3449,478 +3465,478 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>7564.2</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>749</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>+$22.31M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>+$123.96M</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>7574.23</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>+$45.67M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>+$110.03M</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>7544.12</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>747</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>-$15.83M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>+$99.04M</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>7524.05</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5" t="n">
         <v>745</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>-$44.32M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>+$82.47M</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>29414.94</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>710</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>+$3.19M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>+$27.76M</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="5" t="n">
         <v>7473.87</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>740</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>-$21.25M</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>+$25.54M</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>7497.4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7450</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-$18.99M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>+$25.52M</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>29620.55</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>715</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>+$16.34M</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>+$23.12M</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>7497.4</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>7450</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B10" s="5" t="n">
+        <v>7447.4</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7400</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-$16.39M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>+$22.02M</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-$18.62M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>+$20.83M</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>29291.57</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>707</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>+$1.41M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>+$20.36M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>7447.4</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>7400</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="B12" s="5" t="n">
+        <v>7472.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-$19.65M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>+$21.98M</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-$17.24M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+$19.57M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>29291.57</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>707</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="B13" s="5" t="n">
+        <v>29209.33</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>705</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>+$1.41M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>+$20.36M</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>29209.33</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>705</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>+$18.88M</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>7472.4</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>7425</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B14" s="5" t="n">
+        <v>7547.4</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-$16.24M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>+$18.43M</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>4349.9</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>+$16.71M</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>+$17.17M</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$2.34M</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+$18.41M</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3929,36 +3945,40 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>29497.18</v>
+        <v>4349.9</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>712</v>
+        <v>79</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>+$4.78M</t>
+          <t>+$17.36M</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>+$15.72M</t>
+          <t>+$17.81M</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3967,32 +3987,36 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>7547.4</v>
+        <v>7522.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7500</v>
+        <v>7475</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>+$1.92M</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>-$8.74M</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>+$15.11M</t>
+          <t>+$15.86M</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -4001,408 +4025,404 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>29003.72</v>
+        <v>29497.18</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-$11.67M</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>+$4.78M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>+$14.51M</t>
+          <t>+$15.72M</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2977.76</v>
+        <v>29003.72</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>296</v>
+        <v>700</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-$5.33M</t>
+          <t>-$11.67M</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>+$14.36M</t>
+          <t>+$14.51M</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2977.76</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-$5.33M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+$14.36M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B20" s="5" t="n">
         <v>29826.16</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C20" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>+$10.07M</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>+$13.32M</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3018</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>+$10.86M</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>+$12.98M</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>7522.4</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>7475</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="B22" s="5" t="n">
+        <v>7487.4</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>7440</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>-$7.16M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>+$13.00M</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-$10.91M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>+$12.07M</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>3018</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="B23" s="2" t="n">
+        <v>2967.7</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>+$10.86M</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>+$12.98M</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>-$8.94M</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>+$10.72M</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7483.91</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>-$6.87M</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2927.46</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>-$9.77M</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>+$9.84M</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>28798.11</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>695</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>-$8.28M</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>+$8.39M</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>7487.4</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>7440</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="B27" s="5" t="n">
+        <v>7457.4</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>-$9.71M</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>+$10.75M</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>2967.7</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>295</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>-$8.94M</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>+$10.72M</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>7483.91</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>741</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>-$6.87M</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>+$10.10M</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>2927.46</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>291</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-$9.77M</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>+$9.84M</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>7437.4</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>7390</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>-$8.45M</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>+$8.82M</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>28798.11</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>695</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>-$8.28M</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>+$8.39M</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>-$7.61M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+$8.32M</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4415,10 +4435,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7457.4</v>
+        <v>7482.4</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7410</v>
+        <v>7435</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -4427,240 +4447,236 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>-$7.61M</t>
+          <t>-$6.82M</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>+$8.32M</t>
+          <t>+$8.15M</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>29085.97</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>702</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>-$6.61M</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>+$8.03M</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>7437.4</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>7390</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>-$7.78M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+$8.13M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4515.09</v>
+        <v>29085.97</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>82</v>
+        <v>702</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>+$7.65M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>-$6.61M</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>+$7.72M</t>
+          <t>+$8.03M</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4515.09</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>+$7.61M</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>+$7.68M</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>30031.77</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>+$3.05M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>+$7.40M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>7482.4</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>7435</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="B33" s="2" t="n">
+        <v>7517.4</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>7470</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>-$6.25M</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>+$7.47M</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>-$2.60M</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>+$7.33M</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>30031.77</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>725</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>+$3.05M</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>+$7.40M</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B34" s="2" t="n">
         <v>7492.4</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="2" t="n">
         <v>7445</v>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>-$4.78M</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>+$6.01M</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>-$5.45M</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+$6.85M</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>7517.4</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>7470</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>-$2.12M</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>+$5.98M</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4673,29 +4689,29 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>7442.4</v>
+        <v>7572.4</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>7395</v>
+        <v>7525</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>-$4.95M</t>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>+$3.84M</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>+$5.39M</t>
+          <t>+$6.16M</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -4707,146 +4723,150 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>4199.24</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>380</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>-$1.44M</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>+$5.36M</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>7572.4</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>7525</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>7552.4</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>7505</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>+$3.26M</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>+$5.24M</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>-$1.20M</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>+$5.25M</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B38" s="2" t="n">
         <v>29168.21</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="2" t="n">
         <v>704</v>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>-$3.52M</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>+$4.40M</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B39" s="2" t="n">
         <v>7462.4</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C39" s="2" t="n">
         <v>7415</v>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>-$3.89M</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>+$4.32M</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-$3.95M</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+$4.39M</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>7452.4</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>7405</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>-$3.05M</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>+$4.20M</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4855,396 +4875,404 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>7597.4</v>
+        <v>4129.65</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>7550</v>
+        <v>75</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>+$1.49M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>-$3.88M</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>+$4.15M</t>
+          <t>+$4.26M</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>71.04000000000001</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>+$3.85M</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>+$3.99M</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>4155.03</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>376</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>-$3.54M</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>+$4.17M</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4129.65</v>
+        <v>7597.4</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>75</v>
+        <v>7550</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>-$3.53M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>+$1.49M</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>+$3.90M</t>
+          <t>+$4.15M</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>29785.04</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>719</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>+$1.25M</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$3.78M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>7452.4</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>7405</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>-$3.00M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$4.13M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>+$3.85M</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>+$3.99M</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B45" s="2" t="n">
+        <v>29785.04</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>+$1.25M</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>+$3.78M</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>28592.5</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C46" s="2" t="n">
         <v>690</v>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>-$3.62M</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>+$3.70M</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>28386.9</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>685</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-$2.68M</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>+$2.71M</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>2937.52</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>292</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>-$2.46M</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>+$2.57M</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>69.75</v>
+        <v>4177.14</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>108</v>
+        <v>378</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>+$445.61K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>-$2.10M</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>+$2.37M</t>
+          <t>+$3.25M</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>28386.9</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>-$2.68M</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>+$2.71M</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>3909.4</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>-$2.16M</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>+$2.18M</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4155.03</v>
+        <v>2937.52</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>-$1.50M</t>
+          <t>-$2.46M</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>+$2.03M</t>
+          <t>+$2.57M</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>4199.24</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>+$601.96K</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>+$1.82M</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>+$445.61K</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>+$2.37M</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -5253,36 +5281,32 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>4254.49</v>
+        <v>3909.4</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>385</v>
+        <v>71</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>+$1.50M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>-$2.16M</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>+$1.56M</t>
+          <t>+$2.18M</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -5291,10 +5315,10 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>4143.98</v>
+        <v>4254.49</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
@@ -5303,1158 +5327,1166 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>+$320.55K</t>
+          <t>+$1.86M</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>+$1.52M</t>
+          <t>+$1.91M</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>28839.23</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>696</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>-$1.42M</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>+$1.50M</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>-$418.52K</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>+$1.22M</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>4188.19</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>+$416.45K</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>+$1.21M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>4166.09</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>-$151.57K</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>+$1.14M</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>4088.73</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>-$371.00K</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>+$893.93K</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>+$850.11K</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>+$856.86K</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>+$500.56K</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>+$514.55K</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>28839.23</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>696</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-$1.42M</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>+$1.50M</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="B60" s="2" t="n">
+        <v>29368.48</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>29150</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>-$55.43K</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>+$189.62K</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>29418.48</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-$58.35K</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>+$175.04K</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>29508.48</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>29290</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>-$75.85K</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>+$169.20K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>29218.48</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>-$123.40K</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>+$144.41K</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>29528.48</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>29310</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-$78.77K</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>+$125.44K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>29618.48</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>29400</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>+$115.53K</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>29588.48</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>29370</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>-$10.50K</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>+$110.27K</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>29518.48</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>29300</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>+$20.42K</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>+$107.94K</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>-$418.52K</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>+$1.22M</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>29468.48</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>29250</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>-$49.59K</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>+$102.11K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>29558.48</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>29340</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>+$43.76K</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>+$102.11K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>29298.48</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>29080</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-$91.90K</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>+$91.90K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>29358.48</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>29140</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>-$58.35K</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>+$87.52K</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>72.97</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>+$850.11K</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>+$856.86K</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>29388.48</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>29170</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>+$72.93K</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>+$84.60K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>29278.48</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>29060</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-$65.64K</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>+$81.39K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>29248.48</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>29030</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>-$5.25K</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>+$73.52K</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>29268.48</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>29050</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>+$23.63K</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>+$49.89K</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
-        <v>4088.73</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>370</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-$207.67K</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>+$707.05K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="B76" s="2" t="n">
+        <v>4487.56</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>+$42.62K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$49.35K</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>29598.48</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>29380</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-$36.76K</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>+$42.01K</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>29208.48</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>28990</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>+$14.00K</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>+$32.67K</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>29498.48</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>29280</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>+$2.92K</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>+$32.09K</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>29168.48</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>28950</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>-$30.34K</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>+$30.34K</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>74.27</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>+$500.56K</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>+$514.55K</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>4033.48</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>365</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-$307.15K</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>+$346.02K</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>4011.38</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-$218.51K</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>+$220.85K</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>29368.48</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>29150</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="B81" s="2" t="n">
+        <v>29428.48</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>29210</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>-$55.43K</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>+$189.62K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>+$5.83K</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>+$29.17K</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>29418.48</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>29200</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B82" s="2" t="n">
+        <v>29288.48</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>29070</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-$58.35K</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>+$175.04K</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>-$2.63K</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>+$13.13K</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>29508.48</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>29290</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B83" s="2" t="n">
+        <v>29328.48</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>29110</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>-$75.85K</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>+$169.20K</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>29218.48</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>-$123.40K</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>+$144.41K</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>29528.48</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>29310</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>-$78.77K</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>+$125.44K</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>29618.48</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>29400</v>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>+$115.53K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>29588.48</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>29370</v>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>-$10.50K</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>+$110.27K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>29518.48</v>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>29300</v>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>+$20.42K</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>+$107.94K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>+$11.67K</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>29468.48</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>29250</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>-$49.59K</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>+$102.11K</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>29558.48</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>29340</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>+$43.76K</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>+$102.11K</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>29298.48</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>29080</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>-$91.90K</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>+$91.90K</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>29358.48</v>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>29140</v>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>-$58.35K</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>+$87.52K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>29388.48</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>29170</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>+$72.93K</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>+$84.60K</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>29278.48</v>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>29060</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-$65.64K</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>+$81.39K</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>29248.48</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>29030</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>-$5.25K</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>+$73.52K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>29268.48</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>29050</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>+$23.63K</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>+$49.89K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>29598.48</v>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>29380</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-$36.76K</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>+$42.01K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>4487.56</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>+$32.65K</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>+$39.40K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>29208.48</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>28990</v>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>+$14.00K</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>+$32.67K</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>29498.48</v>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>29280</v>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>+$2.92K</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>+$32.09K</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>29168.48</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>28950</v>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-$30.34K</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>+$30.34K</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>29428.48</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>29210</v>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>+$5.83K</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>+$29.17K</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>29288.48</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>29070</v>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-$2.63K</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>+$13.13K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="n">
-        <v>29328.48</v>
-      </c>
-      <c r="C83" s="5" t="n">
-        <v>29110</v>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>+$11.67K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
